--- a/diseases/d242/2020-2025.xlsx
+++ b/diseases/d242/2020-2025.xlsx
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26040,7 +26040,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -36164,7 +36164,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -37746,7 +37746,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -38149,7 +38149,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -39358,7 +39358,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -39761,7 +39761,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -40567,7 +40567,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40970,7 +40970,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -41373,7 +41373,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -49492,7 +49492,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -51074,7 +51074,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51477,7 +51477,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51880,7 +51880,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52283,7 +52283,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52686,7 +52686,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53492,7 +53492,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53895,7 +53895,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54298,7 +54298,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54701,7 +54701,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -55104,7 +55104,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -62427,7 +62427,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -64009,7 +64009,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -64412,7 +64412,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -64815,7 +64815,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -65218,7 +65218,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -65621,7 +65621,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -66024,7 +66024,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -66427,7 +66427,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN334" t="b">
@@ -67233,7 +67233,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -67636,7 +67636,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -68039,7 +68039,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -68442,7 +68442,7 @@
       </c>
       <c r="AM342" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN342" t="b">
@@ -68845,7 +68845,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -69248,7 +69248,7 @@
       </c>
       <c r="AM346" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN346" t="b">
@@ -69651,7 +69651,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN348" t="b">
@@ -70054,7 +70054,7 @@
       </c>
       <c r="AM350" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN350" t="b">
@@ -70457,7 +70457,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -70860,7 +70860,7 @@
       </c>
       <c r="AM354" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN354" t="b">
@@ -71263,7 +71263,7 @@
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN356" t="b">
@@ -71666,7 +71666,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -72069,7 +72069,7 @@
       </c>
       <c r="AM360" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN360" t="b">
@@ -72472,7 +72472,7 @@
       </c>
       <c r="AM362" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN362" t="b">
@@ -72875,7 +72875,7 @@
       </c>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN364" t="b">

--- a/diseases/d242/2020-2025.xlsx
+++ b/diseases/d242/2020-2025.xlsx
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25637,7 +25637,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26040,7 +26040,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -36164,7 +36164,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -37746,7 +37746,7 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN188" t="b">
@@ -38149,7 +38149,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -39358,7 +39358,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -39761,7 +39761,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -40567,7 +40567,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40970,7 +40970,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -41373,7 +41373,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -41776,7 +41776,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -49492,7 +49492,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -51074,7 +51074,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51477,7 +51477,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51880,7 +51880,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52283,7 +52283,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -52686,7 +52686,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53492,7 +53492,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53895,7 +53895,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54298,7 +54298,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54701,7 +54701,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -55104,7 +55104,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -62427,7 +62427,7 @@
       </c>
       <c r="AM312" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN312" t="b">
@@ -64009,7 +64009,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -64412,7 +64412,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -64815,7 +64815,7 @@
       </c>
       <c r="AM324" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN324" t="b">
@@ -65218,7 +65218,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -65621,7 +65621,7 @@
       </c>
       <c r="AM328" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN328" t="b">
@@ -66024,7 +66024,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -66427,7 +66427,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AM334" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN334" t="b">
@@ -67233,7 +67233,7 @@
       </c>
       <c r="AM336" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN336" t="b">
@@ -67636,7 +67636,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -68039,7 +68039,7 @@
       </c>
       <c r="AM340" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN340" t="b">
@@ -68442,7 +68442,7 @@
       </c>
       <c r="AM342" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN342" t="b">
@@ -68845,7 +68845,7 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN344" t="b">
@@ -69248,7 +69248,7 @@
       </c>
       <c r="AM346" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN346" t="b">
@@ -69651,7 +69651,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN348" t="b">
@@ -70054,7 +70054,7 @@
       </c>
       <c r="AM350" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN350" t="b">
@@ -70457,7 +70457,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -70860,7 +70860,7 @@
       </c>
       <c r="AM354" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN354" t="b">
@@ -71263,7 +71263,7 @@
       </c>
       <c r="AM356" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN356" t="b">
@@ -71666,7 +71666,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -72069,7 +72069,7 @@
       </c>
       <c r="AM360" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN360" t="b">
@@ -72472,7 +72472,7 @@
       </c>
       <c r="AM362" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN362" t="b">
@@ -72875,7 +72875,7 @@
       </c>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN364" t="b">
